--- a/data/trans_orig/IP25B01_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Edad-trans_orig.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19144</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39959</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47856</t>
+          <t>47875</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43589</t>
+          <t>43135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52698</t>
+          <t>52541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86506</t>
+          <t>87132</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98266</t>
+          <t>98412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14974</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18078</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26315</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36605</t>
+          <t>36595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54301</t>
+          <t>53921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74708</t>
+          <t>74888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52417</t>
+          <t>53371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74331</t>
+          <t>74971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112779</t>
+          <t>113246</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143004</t>
+          <t>142026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>68506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88573</t>
+          <t>89918</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81662</t>
+          <t>81879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>105245</t>
+          <t>106437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>157296</t>
+          <t>156740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>187367</t>
+          <t>187326</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,57%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35029</t>
+          <t>34546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42247</t>
+          <t>41524</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,47 +1996,47 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>12,4%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>23,99%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>25903</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>17861</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>36514</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>12,19%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>24,41%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>25903</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>17927</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>43307</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70776</t>
+          <t>71950</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65133</t>
+          <t>64650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89675</t>
+          <t>87761</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81435</t>
+          <t>83357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110136</t>
+          <t>110422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153577</t>
+          <t>154090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>191258</t>
+          <t>190852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44569</t>
+          <t>44624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65520</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64056</t>
+          <t>65215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91797</t>
+          <t>92355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115077</t>
+          <t>114520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149044</t>
+          <t>148944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25746</t>
+          <t>25076</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123531</t>
+          <t>116486</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38889</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90066</t>
+          <t>87343</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74336</t>
+          <t>76809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>188698</t>
+          <t>181488</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36413</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68931</t>
+          <t>66619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47469</t>
+          <t>48491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75550</t>
+          <t>75538</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92483</t>
+          <t>90910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134455</t>
+          <t>134913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72493</t>
+          <t>74719</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120170</t>
+          <t>121244</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>106640</t>
+          <t>106309</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>147458</t>
+          <t>146929</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>194282</t>
+          <t>193456</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>258421</t>
+          <t>256339</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44775</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83336</t>
+          <t>81686</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44391</t>
+          <t>44163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72359</t>
+          <t>71543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96534</t>
+          <t>99771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142957</t>
+          <t>144208</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40257</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>152464</t>
+          <t>160064</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>57571</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113910</t>
+          <t>115881</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108760</t>
+          <t>111108</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>234273</t>
+          <t>238409</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74195</t>
+          <t>72606</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>112022</t>
+          <t>109903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88325</t>
+          <t>87914</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123518</t>
+          <t>124397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171508</t>
+          <t>175662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>224686</t>
+          <t>227935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>212103</t>
+          <t>214427</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>271225</t>
+          <t>274063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>267664</t>
+          <t>268184</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>320955</t>
+          <t>321684</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>500908</t>
+          <t>500241</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>580998</t>
+          <t>578389</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>209396</t>
+          <t>208013</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>267429</t>
+          <t>266894</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>251124</t>
+          <t>251236</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>300815</t>
+          <t>303049</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>476781</t>
+          <t>474665</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>554660</t>
+          <t>559719</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B01_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos entre semana / solo 2023 en 2023 (tasa de respuesta: 98,33%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos entre semana en 2023 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3729</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4996</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3472</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4622</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2203</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2244</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1824</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6334</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5437</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2921</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6352</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3508</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10744</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11133</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40422</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36580</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43495</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>84,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>76,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>44796</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>40171</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47875</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>86,86%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>77,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48559</t>
+          <t>39773</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43135</t>
+          <t>35499</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52541</t>
+          <t>43028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>93355</t>
+          <t>80194</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87132</t>
+          <t>74432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98412</t>
+          <t>84853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47830</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47830</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47830</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>51573</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>51573</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51573</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>58376</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58376</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58376</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>94514</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>94514</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>94514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18486</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13898</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9488</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20776</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8527</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4443</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14298</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25813</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36595</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55995</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46391</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>66048</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>64156</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53921</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74888</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>41,38%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62962</t>
+          <t>57644</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53371</t>
+          <t>48923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74971</t>
+          <t>66740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>127118</t>
+          <t>113639</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113246</t>
+          <t>100472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142026</t>
+          <t>126838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>80890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70864</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>90673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>51,49%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>57,72%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>78566</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>68506</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>89918</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>50,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>44,18%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>57,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94446</t>
+          <t>72072</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81879</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106437</t>
+          <t>81073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>173012</t>
+          <t>152962</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>156740</t>
+          <t>139554</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>187326</t>
+          <t>166716</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>157091</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>157091</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>157091</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>155052</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>155052</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>155052</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>182060</t>
+          <t>141659</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182060</t>
+          <t>141659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182060</t>
+          <t>141659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>337112</t>
+          <t>298750</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>337112</t>
+          <t>298750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>337112</t>
+          <t>298750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12049</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19689</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>12512</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7829</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20003</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>19651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>25079</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34546</t>
+          <t>35671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24415</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16367</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>33279</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>16,63%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30014</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>21453</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>41524</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>12,4%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>28715</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36514</t>
+          <t>38582</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>55918</t>
+          <t>53129</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>44629</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>71950</t>
+          <t>66658</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>89202</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>74606</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>101269</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>50,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>75595</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>64650</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>87761</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,68%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,35%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>96369</t>
+          <t>76738</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83357</t>
+          <t>65654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110422</t>
+          <t>88419</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>171965</t>
+          <t>165940</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154090</t>
+          <t>148391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190852</t>
+          <t>182171</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>74460</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>61322</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>88273</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,64%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>54950</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>44624</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>66743</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>31,75%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77711</t>
+          <t>56189</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65215</t>
+          <t>46103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92355</t>
+          <t>66608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>132662</t>
+          <t>130649</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114520</t>
+          <t>114616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148944</t>
+          <t>146927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>49419</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>35190</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>74172</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17,09%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>52375</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>25076</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>116486</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>42,94%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56676</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39819</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87343</t>
+          <t>41212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>109051</t>
+          <t>78454</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76809</t>
+          <t>60614</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>181488</t>
+          <t>110640</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60417</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>47586</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>74817</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,46%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>25,88%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>52875</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>35881</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>66619</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>19,49%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,56%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61004</t>
+          <t>53994</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48491</t>
+          <t>43684</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75538</t>
+          <t>68354</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>113879</t>
+          <t>114412</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90910</t>
+          <t>96866</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134913</t>
+          <t>133357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>125505</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>107751</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>143814</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>43,41%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>49,74%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>101862</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>74719</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>121244</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>37,55%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>27,54%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>127821</t>
+          <t>107849</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>106309</t>
+          <t>93437</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>146929</t>
+          <t>122680</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>229683</t>
+          <t>233354</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>193456</t>
+          <t>209122</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>256339</t>
+          <t>255649</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>47,23%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>53801</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>41875</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>66098</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>22,86%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>64185</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>45580</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>81686</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>30,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>56634</t>
+          <t>61236</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>49110</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71543</t>
+          <t>74084</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>120819</t>
+          <t>115036</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99771</t>
+          <t>98554</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144208</t>
+          <t>134263</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>289143</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>289143</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>289143</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>271297</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>271297</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>271297</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>302135</t>
+          <t>252114</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>302135</t>
+          <t>252114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302135</t>
+          <t>252114</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>573432</t>
+          <t>541257</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>573432</t>
+          <t>541257</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>573432</t>
+          <t>541257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>68791</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>51871</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>100354</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>68690</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>40413</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>160064</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>77863</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57571</t>
+          <t>34911</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>115881</t>
+          <t>59058</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>146553</t>
+          <t>114766</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111108</t>
+          <t>95411</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>238409</t>
+          <t>148465</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>99687</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>83914</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>118822</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>91842</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>72606</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>109903</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>16,88%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>106017</t>
+          <t>91190</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87914</t>
+          <t>75460</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>124397</t>
+          <t>107556</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>197859</t>
+          <t>190877</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175662</t>
+          <t>167559</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>227935</t>
+          <t>215588</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>276140</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>250839</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>300646</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>366</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>247965</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>214427</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>274063</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>38,09%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>42,1%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>293829</t>
+          <t>248695</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268184</t>
+          <t>227158</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>321684</t>
+          <t>266924</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>541795</t>
+          <t>524834</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>500241</t>
+          <t>491685</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>578389</t>
+          <t>556119</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>249572</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>225149</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>272680</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>32,43%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>242497</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>208013</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>266894</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>277350</t>
+          <t>229270</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>251236</t>
+          <t>211344</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>303049</t>
+          <t>251830</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>519847</t>
+          <t>478842</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>474665</t>
+          <t>446733</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>559719</t>
+          <t>508862</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>919</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>650994</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>650994</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>650994</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>615130</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>615130</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>615130</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1406055</t>
+          <t>1309319</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1406055</t>
+          <t>1309319</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1406055</t>
+          <t>1309319</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
